--- a/docs/Milestone4/CST-452_Traceability_Matrix_SecureLink_M4.xlsx
+++ b/docs/Milestone4/CST-452_Traceability_Matrix_SecureLink_M4.xlsx
@@ -834,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.15625" defaultRowHeight="13" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3.15" customWidth="1" style="43" min="1" max="1"/>
@@ -971,7 +971,7 @@
       </c>
       <c r="F5" s="77" t="inlineStr">
         <is>
-          <t>TC-AUTH-01, TC-AUTH-02</t>
+          <t>TC-AUTH-01, TC-AUTH-02, TC-AUTH-05</t>
         </is>
       </c>
       <c r="G5" s="78" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F6" s="84" t="inlineStr">
         <is>
-          <t>TC-AUTH-03, TC-AUTH-04</t>
+          <t>TC-AUTH-03, TC-AUTH-04, TC-AUTH-06</t>
         </is>
       </c>
       <c r="G6" s="78" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="B8" s="81" t="inlineStr"/>
       <c r="C8" s="82" t="inlineStr">
         <is>
-          <t>User selects relay region (Virginia/US-East or Germany) and connects</t>
+          <t>User selects relay region (New York/US-East or Germany) and connects</t>
         </is>
       </c>
       <c r="D8" s="82" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F8" s="84" t="inlineStr">
         <is>
-          <t>TC-SESS-02, TC-SESS-03</t>
+          <t>TC-SESS-02, TC-SESS-03, TC-SSH-03, TC-SSH-06</t>
         </is>
       </c>
       <c r="G8" s="78" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F10" s="84" t="inlineStr">
         <is>
-          <t>TC-RELAY-01, TC-RELAY-02</t>
+          <t>TC-RELAY-01, TC-RELAY-02, TC-SSH-03, TC-SSH-04, TC-SSH-05</t>
         </is>
       </c>
       <c r="G10" s="78" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="F18" s="84" t="inlineStr">
         <is>
-          <t>TC-ADM-01</t>
+          <t>TC-ADM-01, TC-ADM-03</t>
         </is>
       </c>
       <c r="G18" s="78" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="F19" s="84" t="inlineStr">
         <is>
-          <t>TC-ADM-02</t>
+          <t>TC-ADM-02, TC-ADM-03, TC-ADM-04</t>
         </is>
       </c>
       <c r="G19" s="78" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G20" s="78" t="inlineStr">
         <is>
-          <t>nyc3 stands in for "Virginia"/US-East — DigitalOcean has no literal Virginia region.</t>
+          <t>nyc3 = New York (US-East); region key "newyork".</t>
         </is>
       </c>
       <c r="H20" s="79" t="n"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G22" s="78" t="inlineStr">
         <is>
-          <t>Not implemented yet — currently an in-memory field only. Planned for a later milestone.</t>
+          <t>Not implemented yet — currently an in-memory field only. Planned for a later milestone. Out of scope for Milestone 5 testing; planned for Milestone 6.</t>
         </is>
       </c>
       <c r="H22" s="79" t="n"/>
@@ -1610,14 +1610,82 @@
       </c>
       <c r="G23" s="78" t="inlineStr">
         <is>
-          <t>Stub only — checks for "any output," doesn't yet compare timestamps or surface an alert.</t>
+          <t>Stub only — checks for "any output," doesn't yet compare timestamps or surface an alert. Out of scope for Milestone 5 testing; planned for Milestone 6.</t>
         </is>
       </c>
       <c r="H23" s="79" t="n"/>
       <c r="I23" s="80" t="n"/>
     </row>
-    <row r="24" ht="14" customHeight="1" s="72"/>
-    <row r="25" ht="14" customHeight="1" s="72"/>
+    <row r="24" ht="45" customHeight="1" s="72">
+      <c r="A24" s="85" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B24" s="81" t="n"/>
+      <c r="C24" s="82" t="inlineStr">
+        <is>
+          <t>User disconnects their own session on demand; cannot end another user's session</t>
+        </is>
+      </c>
+      <c r="D24" s="82" t="inlineStr">
+        <is>
+          <t>SDD §3.x Session Management</t>
+        </is>
+      </c>
+      <c r="E24" s="83" t="inlineStr">
+        <is>
+          <t>SessionsController.Disconnect(); RelayGatewayService.RemovePeerAsync()</t>
+        </is>
+      </c>
+      <c r="F24" s="84" t="inlineStr">
+        <is>
+          <t>TC-SESS-06, TC-SESS-07</t>
+        </is>
+      </c>
+      <c r="G24" s="78" t="inlineStr">
+        <is>
+          <t>Disconnect is idempotent; another user's session id returns 404.</t>
+        </is>
+      </c>
+      <c r="H24" s="79" t="n"/>
+      <c r="I24" s="80" t="n"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" s="72">
+      <c r="A25" s="85" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="B25" s="81" t="n"/>
+      <c r="C25" s="82" t="inlineStr">
+        <is>
+          <t>Backend reaches the Germany relay's management API through a supervised, key-authenticated SSH tunnel</t>
+        </is>
+      </c>
+      <c r="D25" s="82" t="inlineStr">
+        <is>
+          <t>README.md – Architecture diagram ("SSH tunnel for Germany")</t>
+        </is>
+      </c>
+      <c r="E25" s="83" t="inlineStr">
+        <is>
+          <t>germany-mgmt-tunnel.service on the US relay; appsettings.json Relays[germany].ManagementUrl = 127.0.0.1:8788</t>
+        </is>
+      </c>
+      <c r="F25" s="84" t="inlineStr">
+        <is>
+          <t>TC-SSH-01, TC-SSH-02, TC-SSH-07, TC-SSH-08</t>
+        </is>
+      </c>
+      <c r="G25" s="78" t="inlineStr">
+        <is>
+          <t>Restart=always; unit lives on the server, not in the repo.</t>
+        </is>
+      </c>
+      <c r="H25" s="79" t="n"/>
+      <c r="I25" s="80" t="n"/>
+    </row>
     <row r="26" ht="14" customHeight="1" s="72"/>
     <row r="27" ht="14" customHeight="1" s="72"/>
     <row r="28" ht="14" customHeight="1" s="72"/>
